--- a/fuction_ensemble_3/media_ponderada/metricas_ensemble_filtrado.xlsx
+++ b/fuction_ensemble_3/media_ponderada/metricas_ensemble_filtrado.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>linha</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>mse_1000_original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>mse_1000_f</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>r2_1000_f</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>mse_25_f</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>r2_25_f</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>var_f</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>bias_f</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>covar_f</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>num_redes_total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>num_redes_filtradas</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>nomes_redes_filtradas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pesos_filtrados</t>
         </is>
@@ -1043,40 +1031,40 @@
         <v>1732.883251164641</v>
       </c>
       <c r="C14" t="n">
-        <v>1757.508400257924</v>
+        <v>1749.342857904222</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9953443486085882</v>
+        <v>0.9953659791843597</v>
       </c>
       <c r="E14" t="n">
-        <v>696.486625921759</v>
+        <v>736.5175974933575</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9981550023154391</v>
+        <v>0.9980489600066401</v>
       </c>
       <c r="G14" t="n">
-        <v>244.395758065923</v>
+        <v>110.4579707614541</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.844235220568438</v>
+        <v>-6.939450588444339</v>
       </c>
       <c r="I14" t="n">
-        <v>367760.4923742817</v>
+        <v>371103.5167823608</v>
       </c>
       <c r="J14" t="n">
         <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_31_9_8.xlsx', '1000_model_35_7_20.xlsx', '1000_model_38_2_0.xlsx']</t>
+          <t>['1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_31_9_8.xlsx', '1000_model_38_2_0.xlsx']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>[0.20482596 0.20482596 0.16376399 0.2523379  0.04976542 0.12448076]</t>
+          <t>[0.21555305 0.21555305 0.17234059 0.26555327 0.13100003]</t>
         </is>
       </c>
     </row>
@@ -1403,40 +1391,40 @@
         <v>1761.0153214006</v>
       </c>
       <c r="C22" t="n">
-        <v>1761.01532049057</v>
+        <v>1751.658977103318</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9953350587536673</v>
+        <v>0.9953598437692628</v>
       </c>
       <c r="E22" t="n">
-        <v>744.9194038681719</v>
+        <v>781.9410223502601</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9980267035659122</v>
+        <v>0.9979286330533768</v>
       </c>
       <c r="G22" t="n">
-        <v>109.9717032194432</v>
+        <v>118.4481761782136</v>
       </c>
       <c r="H22" t="n">
-        <v>-7.028491623424807</v>
+        <v>-7.202784303682796</v>
       </c>
       <c r="I22" t="n">
-        <v>371103.5167823608</v>
+        <v>370489.4917146912</v>
       </c>
       <c r="J22" t="n">
         <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>['1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_31_9_8.xlsx', '1000_model_38_2_0.xlsx']</t>
+          <t>['1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_31_9_8.xlsx']</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>[0.23068727 0.23068727 0.19941753 0.24032934 0.09887858]</t>
+          <t>[0.25600021 0.25600021 0.22129929 0.26670029]</t>
         </is>
       </c>
     </row>
@@ -1448,41 +1436,40 @@
         <v>1794.206673219672</v>
       </c>
       <c r="C23" t="n">
-        <v>1794.206811750548</v>
+        <v>1771.598992313104</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9952471342735085</v>
+        <v>0.9953070225369189</v>
       </c>
       <c r="E23" t="n">
-        <v>326.6825247948638</v>
+        <v>714.3082466295148</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9991346158283579</v>
+        <v>0.9981077927241603</v>
       </c>
       <c r="G23" t="n">
-        <v>288.671667354433</v>
+        <v>108.9388955950492</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.505372375047775</v>
+        <v>-6.883318257144256</v>
       </c>
       <c r="I23" t="n">
-        <v>369962.0252893365</v>
+        <v>371103.5167823608</v>
       </c>
       <c r="J23" t="n">
         <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1000_model_18_4_11.xlsx', '1000_model_18_4_20.xlsx', '1000_model_21_9_0.xlsx', '1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_29_6_0.xlsx', '1000_model_31_9_8.xlsx', '1000_model_35_7_20.xlsx', '1000_model_38_2_0.xlsx']</t>
+          <t>['1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_31_9_8.xlsx', '1000_model_38_2_0.xlsx']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>[0.07248574 0.07248574 0.07273696 0.12503311 0.12503311 0.11866145
- 0.08035574 0.13127689 0.09003761 0.11189367]</t>
+          <t>[0.20433645 0.20433645 0.19392351 0.2145404  0.1828632 ]</t>
         </is>
       </c>
     </row>
@@ -1494,41 +1481,40 @@
         <v>1824.073048292828</v>
       </c>
       <c r="C24" t="n">
-        <v>1824.072987400525</v>
+        <v>1775.228643056109</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9951680185764225</v>
+        <v>0.9952974075680633</v>
       </c>
       <c r="E24" t="n">
-        <v>277.3753844018795</v>
+        <v>710.7339586202227</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9992652307697963</v>
+        <v>0.9981172610367676</v>
       </c>
       <c r="G24" t="n">
-        <v>281.9228904715554</v>
+        <v>108.8734879462857</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.089197571558798</v>
+        <v>-6.872568930357477</v>
       </c>
       <c r="I24" t="n">
-        <v>369962.0252893365</v>
+        <v>371103.5167823608</v>
       </c>
       <c r="J24" t="n">
         <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>['1000_model_18_4_11.xlsx', '1000_model_18_4_20.xlsx', '1000_model_21_9_0.xlsx', '1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_29_6_0.xlsx', '1000_model_31_9_8.xlsx', '1000_model_35_7_20.xlsx', '1000_model_38_2_0.xlsx']</t>
+          <t>['1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_31_9_8.xlsx', '1000_model_38_2_0.xlsx']</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>[0.0870142  0.0870142  0.08714112 0.11154011 0.11154011 0.10883958
- 0.09106683 0.11413383 0.09582855 0.10588146]</t>
+          <t>[0.20208918 0.20208918 0.19719634 0.2067885  0.1918368 ]</t>
         </is>
       </c>
     </row>
@@ -1540,41 +1526,40 @@
         <v>1852.445736088406</v>
       </c>
       <c r="C25" t="n">
-        <v>1852.445682152742</v>
+        <v>1778.149539011594</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9950928591201252</v>
+        <v>0.9952896700953335</v>
       </c>
       <c r="E25" t="n">
-        <v>242.0191794126362</v>
+        <v>707.8542062489694</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9993588895909599</v>
+        <v>0.9981248895198703</v>
       </c>
       <c r="G25" t="n">
-        <v>280.0858836606783</v>
+        <v>108.8552763515691</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.761253696495792</v>
+        <v>-6.863537378773765</v>
       </c>
       <c r="I25" t="n">
-        <v>369962.0252893365</v>
+        <v>371103.5167823608</v>
       </c>
       <c r="J25" t="n">
         <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['1000_model_18_4_11.xlsx', '1000_model_18_4_20.xlsx', '1000_model_21_9_0.xlsx', '1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_29_6_0.xlsx', '1000_model_31_9_8.xlsx', '1000_model_35_7_20.xlsx', '1000_model_38_2_0.xlsx']</t>
+          <t>['1000_model_24_8_4.xlsx', '1000_model_24_9_14.xlsx', '1000_model_26_8_14.xlsx', '1000_model_31_9_8.xlsx', '1000_model_38_2_0.xlsx']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>[0.09869179 0.09869179 0.09870685 0.10113127 0.10113127 0.1008887
- 0.0991395  0.10135908 0.09964058 0.10061916]</t>
+          <t>[0.20020861 0.20020861 0.19972839 0.2006596  0.19919479]</t>
         </is>
       </c>
     </row>
@@ -1586,40 +1571,40 @@
         <v>1722.948334205656</v>
       </c>
       <c r="C26" t="n">
-        <v>1710.803442406798</v>
+        <v>1738.921974365616</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9954680703512403</v>
+        <v>0.9953935841738659</v>
       </c>
       <c r="E26" t="n">
-        <v>596.9702804112742</v>
+        <v>644.1394884383276</v>
       </c>
       <c r="F26" t="n">
-        <v>0.998418621773745</v>
+        <v>0.9982936702293025</v>
       </c>
       <c r="G26" t="n">
-        <v>149.7739191206545</v>
+        <v>137.3865536437616</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.010697422033692</v>
+        <v>-6.082630951258261</v>
       </c>
       <c r="I26" t="n">
-        <v>369356.9126287993</v>
+        <v>367021.195553707</v>
       </c>
       <c r="J26" t="n">
         <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>[0.33502723 0.09519873 0.23460102 0.33517302]</t>
+          <t>[0.37027714 0.25928458 0.37043827]</t>
         </is>
       </c>
     </row>
@@ -1631,40 +1616,40 @@
         <v>1737.74645004991</v>
       </c>
       <c r="C27" t="n">
-        <v>1738.017471645403</v>
+        <v>1744.809172699147</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9953959802075618</v>
+        <v>0.9953779889464923</v>
       </c>
       <c r="E27" t="n">
-        <v>579.4227774906224</v>
+        <v>668.129031158156</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9984651052251904</v>
+        <v>0.9982301217717665</v>
       </c>
       <c r="G27" t="n">
-        <v>268.731059801643</v>
+        <v>142.4234045628253</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.011281230775229</v>
+        <v>-6.166193387354302</v>
       </c>
       <c r="I27" t="n">
-        <v>365750.6087560305</v>
+        <v>367021.195553707</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>[0.3308433  0.09835844 0.06348277 0.17606292 0.33125257]</t>
+          <t>[0.39472628 0.21005915 0.39521457]</t>
         </is>
       </c>
     </row>
@@ -1721,40 +1706,40 @@
         <v>1741.802435106074</v>
       </c>
       <c r="C29" t="n">
-        <v>1745.955621514226</v>
+        <v>1743.730743203775</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9953749519959888</v>
+        <v>0.9953808457133675</v>
       </c>
       <c r="E29" t="n">
-        <v>844.4341633164595</v>
+        <v>849.537514771782</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9977630883090954</v>
+        <v>0.9977495694972933</v>
       </c>
       <c r="G29" t="n">
-        <v>54.21518257295774</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.63930716873348</v>
+        <v>-5.577232666015643</v>
       </c>
       <c r="I29" t="n">
-        <v>371170.6208219208</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1000_model_24_9_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>[0.03276284 0.96723716]</t>
+          <t>[1.]</t>
         </is>
       </c>
     </row>
@@ -2261,40 +2246,40 @@
         <v>1748.27045681987</v>
       </c>
       <c r="C41" t="n">
-        <v>1747.12659847431</v>
+        <v>1750.49151305548</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9953718500702667</v>
+        <v>0.995362936389257</v>
       </c>
       <c r="E41" t="n">
-        <v>576.7197723930475</v>
+        <v>684.8924369035908</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9984722655035946</v>
+        <v>0.9981857153989309</v>
       </c>
       <c r="G41" t="n">
-        <v>267.9868913406287</v>
+        <v>146.9765483906784</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.025465282434578</v>
+        <v>-6.218161084183159</v>
       </c>
       <c r="I41" t="n">
-        <v>365750.6087560305</v>
+        <v>367021.195553707</v>
       </c>
       <c r="J41" t="n">
         <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>[0.33262874 0.10357282 0.08422647 0.14495021 0.33462176]</t>
+          <t>[0.40954007 0.178466   0.41199393]</t>
         </is>
       </c>
     </row>
@@ -2351,40 +2336,40 @@
         <v>1778.332186929842</v>
       </c>
       <c r="C43" t="n">
-        <v>1783.004785516154</v>
+        <v>1814.040073116782</v>
       </c>
       <c r="D43" t="n">
-        <v>0.995276808515189</v>
+        <v>0.9951945958328032</v>
       </c>
       <c r="E43" t="n">
-        <v>750.8241932194341</v>
+        <v>798.881605413467</v>
       </c>
       <c r="F43" t="n">
-        <v>0.998011061739816</v>
+        <v>0.997883757336653</v>
       </c>
       <c r="G43" t="n">
-        <v>170.7085040168515</v>
+        <v>28.94384988364977</v>
       </c>
       <c r="H43" t="n">
-        <v>-6.399467706942558</v>
+        <v>-6.516779878602668</v>
       </c>
       <c r="I43" t="n">
-        <v>367021.195553707</v>
+        <v>371170.6208219208</v>
       </c>
       <c r="J43" t="n">
         <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['1000_model_24_9_0.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>[0.46159216 0.06916753 0.46924032]</t>
+          <t>[0.49589176 0.50410824]</t>
         </is>
       </c>
     </row>
@@ -2486,41 +2471,40 @@
         <v>1817.963285138217</v>
       </c>
       <c r="C46" t="n">
-        <v>1817.963202351034</v>
+        <v>1693.463517845167</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9951842034374807</v>
+        <v>0.995514003926238</v>
       </c>
       <c r="E46" t="n">
-        <v>316.9460936470856</v>
+        <v>573.2033610825905</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9991604076989481</v>
+        <v>0.9984815805004434</v>
       </c>
       <c r="G46" t="n">
-        <v>276.5301227893312</v>
+        <v>147.0959960502484</v>
       </c>
       <c r="H46" t="n">
-        <v>-4.308527073672043</v>
+        <v>-5.989062238689687</v>
       </c>
       <c r="I46" t="n">
-        <v>370085.7996647715</v>
+        <v>369356.9126287993</v>
       </c>
       <c r="J46" t="n">
         <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['1000_model_14_9_19.xlsx', '1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_29_6_0.xlsx', '1000_model_30_8_1.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_37_9_24.xlsx', '1000_model_7_9_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>[0.04952794 0.20805536 0.10956755 0.06106965 0.04156904 0.09903314
- 0.12821111 0.05112933 0.04257988 0.20925699]</t>
+          <t>[0.31759764 0.16725546 0.19571496 0.31943194]</t>
         </is>
       </c>
     </row>
@@ -2532,41 +2516,40 @@
         <v>1958.719337032346</v>
       </c>
       <c r="C47" t="n">
-        <v>1958.719337032346</v>
+        <v>1809.662542707138</v>
       </c>
       <c r="D47" t="n">
-        <v>0.99481133950455</v>
+        <v>0.9952061919398486</v>
       </c>
       <c r="E47" t="n">
-        <v>179.9318663568054</v>
+        <v>472.896652901443</v>
       </c>
       <c r="F47" t="n">
-        <v>0.999523359294419</v>
+        <v>0.9987472936346982</v>
       </c>
       <c r="G47" t="n">
-        <v>235.7696642923217</v>
+        <v>232.4645365554075</v>
       </c>
       <c r="H47" t="n">
-        <v>-3.010465274797365</v>
+        <v>-5.690536301987477</v>
       </c>
       <c r="I47" t="n">
-        <v>370085.7996647715</v>
+        <v>365750.6087560305</v>
       </c>
       <c r="J47" t="n">
         <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1000_model_14_9_19.xlsx', '1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_29_6_0.xlsx', '1000_model_30_8_1.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_37_9_24.xlsx', '1000_model_7_9_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>[0.08785664 0.12165588 0.10587982 0.09241996 0.08393116 0.10369463
- 0.10983757 0.08847054 0.08451524 0.12173856]</t>
+          <t>[0.21615935 0.1881283  0.18424563 0.19516046 0.21630626]</t>
         </is>
       </c>
     </row>
@@ -2578,41 +2561,40 @@
         <v>1987.952370825964</v>
       </c>
       <c r="C48" t="n">
-        <v>1987.952317791586</v>
+        <v>1818.222243860498</v>
       </c>
       <c r="D48" t="n">
-        <v>0.994733901144923</v>
+        <v>0.9951835172348066</v>
       </c>
       <c r="E48" t="n">
-        <v>161.3903082624382</v>
+        <v>467.2804574806235</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9995724760046029</v>
+        <v>0.9987621709735612</v>
       </c>
       <c r="G48" t="n">
-        <v>234.0309461392793</v>
+        <v>232.0262510367854</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.789248304726783</v>
+        <v>-5.665771966065329</v>
       </c>
       <c r="I48" t="n">
-        <v>370085.7996647715</v>
+        <v>365750.6087560305</v>
       </c>
       <c r="J48" t="n">
         <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1000_model_14_9_19.xlsx', '1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_29_6_0.xlsx', '1000_model_30_8_1.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_37_9_24.xlsx', '1000_model_7_9_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>[0.09448684 0.10966068 0.10282992 0.0966641  0.09258462 0.10184712
- 0.10457599 0.09478554 0.09286789 0.10969729]</t>
+          <t>[0.20745062 0.19452853 0.19266932 0.19783166 0.20751988]</t>
         </is>
       </c>
     </row>
@@ -2624,41 +2606,40 @@
         <v>2010.985860697741</v>
       </c>
       <c r="C49" t="n">
-        <v>2010.985811923294</v>
+        <v>1825.239314170956</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9946728852664284</v>
+        <v>0.9951649289690836</v>
       </c>
       <c r="E49" t="n">
-        <v>148.2937277071635</v>
+        <v>463.1581896564628</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9996071689332261</v>
+        <v>0.9987730908883272</v>
       </c>
       <c r="G49" t="n">
-        <v>233.5881588451034</v>
+        <v>231.9083544910975</v>
       </c>
       <c r="H49" t="n">
-        <v>-2.623313977283242</v>
+        <v>-5.646665134068538</v>
       </c>
       <c r="I49" t="n">
-        <v>370085.7996647715</v>
+        <v>365750.6087560305</v>
       </c>
       <c r="J49" t="n">
         <v>10</v>
       </c>
       <c r="K49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1000_model_14_9_19.xlsx', '1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_29_6_0.xlsx', '1000_model_30_8_1.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_37_9_24.xlsx', '1000_model_7_9_0.xlsx', '1000_model_8_4_3.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_28_9_21.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx', '1000_model_8_4_3.xlsx']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>[0.09946191 0.10092623 0.10029316 0.09968538 0.09926125 0.1001993
- 0.10045928 0.09949249 0.09929167 0.10092932]</t>
+          <t>[0.20072547 0.1994664  0.19927973 0.19979678 0.20073162]</t>
         </is>
       </c>
     </row>
@@ -2670,40 +2651,40 @@
         <v>1819.347876322069</v>
       </c>
       <c r="C50" t="n">
-        <v>1817.059981748144</v>
+        <v>1850.918457216438</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9951865960748394</v>
+        <v>0.9950969047490955</v>
       </c>
       <c r="E50" t="n">
-        <v>611.855296540703</v>
+        <v>653.628146255372</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9983791912674419</v>
+        <v>0.9982685347119064</v>
       </c>
       <c r="G50" t="n">
-        <v>145.8536434636873</v>
+        <v>130.1435294304825</v>
       </c>
       <c r="H50" t="n">
-        <v>-6.7257275785925</v>
+        <v>-6.849949612311629</v>
       </c>
       <c r="I50" t="n">
-        <v>370201.7144708151</v>
+        <v>368148.4697033504</v>
       </c>
       <c r="J50" t="n">
         <v>10</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['1000_model_24_9_0.xlsx', '1000_model_24_9_5.xlsx', '1000_model_28_9_21.xlsx', '1000_model_36_5_0.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_24_9_5.xlsx', '1000_model_36_5_0.xlsx']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>[0.35148758 0.35148758 0.08156763 0.21545721]</t>
+          <t>[0.38270383 0.38270383 0.23459235]</t>
         </is>
       </c>
     </row>
@@ -2715,40 +2696,40 @@
         <v>1830.203607224405</v>
       </c>
       <c r="C51" t="n">
-        <v>1843.509753552507</v>
+        <v>1879.58190257753</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9951165304541656</v>
+        <v>0.9950209750925099</v>
       </c>
       <c r="E51" t="n">
-        <v>595.4209765121883</v>
+        <v>698.6143310378653</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9984227258900339</v>
+        <v>0.9981493660104958</v>
       </c>
       <c r="G51" t="n">
-        <v>276.025476052266</v>
+        <v>142.61413594711</v>
       </c>
       <c r="H51" t="n">
-        <v>-6.749947341225861</v>
+        <v>-7.062261829630866</v>
       </c>
       <c r="I51" t="n">
-        <v>366424.908309589</v>
+        <v>368148.4697033504</v>
       </c>
       <c r="J51" t="n">
         <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['1000_model_24_9_0.xlsx', '1000_model_24_9_5.xlsx', '1000_model_28_9_21.xlsx', '1000_model_35_7_20.xlsx', '1000_model_36_5_0.xlsx']</t>
+          <t>['1000_model_24_9_0.xlsx', '1000_model_24_9_5.xlsx', '1000_model_36_5_0.xlsx']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>[0.35190909 0.35190909 0.09591918 0.07164263 0.12862001]</t>
+          <t>[0.42274501 0.42274501 0.15450998]</t>
         </is>
       </c>
     </row>
